--- a/backend/attendance.xlsx
+++ b/backend/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,40 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>17:12:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Karan_Rajput</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16:56:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kartik_Bawankar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>27-05-2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16:56:20</t>
         </is>
       </c>
     </row>
